--- a/corpus/C07.xlsx
+++ b/corpus/C07.xlsx
@@ -3577,8 +3577,8 @@
         <v>826276.0</v>
       </c>
       <c r="AA15">
-        <f>SUM(C15:Z15)</f>
-        <v>13578604.0</v>
+        <f>SUM(C15:Y15)</f>
+        <v>12752328.0</v>
       </c>
     </row>
     <row r="16">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>13578604.0</v>
+        <v>12752328.0</v>
       </c>
     </row>
     <row r="5">
